--- a/results/Int All Data -0.1/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_5_permute.xlsx
@@ -440,567 +440,567 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9903314064429229</v>
+        <v>0.989316047442661</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.989691136304112</v>
+        <v>0.989316047442661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.989691136304112</v>
+        <v>0.989316047442661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.990353387959741</v>
+        <v>0.9889629400980282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9905965877202829</v>
+        <v>0.9889629400980282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9898903730310173</v>
+        <v>0.9886098327533954</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.98920613985857</v>
+        <v>0.9900222621319266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.98920613985857</v>
+        <v>0.9886098327533954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9895592472032028</v>
+        <v>0.9889629400980282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9892281213753882</v>
+        <v>0.9910376211321884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9892281213753882</v>
+        <v>0.9903753694765592</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.989581228720021</v>
+        <v>0.9907064953043738</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9872853294421371</v>
+        <v>0.9907064953043738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9872853294421371</v>
+        <v>0.9907064953043738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.987263347925319</v>
+        <v>0.9907064953043738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9882567254087626</v>
+        <v>0.9903973509933774</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9872413664085008</v>
+        <v>0.9903973509933774</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9862479889250571</v>
+        <v>0.9913907284768212</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9868662775470498</v>
+        <v>0.9910376211321884</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9862040258914206</v>
+        <v>0.991368746960003</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9858948815804243</v>
+        <v>0.9907064953043738</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9865571332360534</v>
+        <v>0.9900442436487447</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9865571332360534</v>
+        <v>0.9903753694765592</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9854978112021551</v>
+        <v>0.9903753694765592</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9871974033748643</v>
+        <v>0.9910376211321884</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9874625846522244</v>
+        <v>0.9883886145096719</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9873966401017698</v>
+        <v>0.9870860927152318</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9866684438956861</v>
+        <v>0.987748344370861</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9884559621356681</v>
+        <v>0.9880574886818573</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9877497474464025</v>
+        <v>0.9890069031316646</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9877497474464025</v>
+        <v>0.98867577730385</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9852779960339731</v>
+        <v>0.9893380289594792</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9849029071725222</v>
+        <v>0.9856956448535189</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9827622815879073</v>
+        <v>0.9860267706813335</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9845497998278894</v>
+        <v>0.9863798780259663</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9849029071725222</v>
+        <v>0.9853645190257043</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9849029071725222</v>
+        <v>0.9849894301642534</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9796722415534852</v>
+        <v>0.9830246567141842</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9809967448647434</v>
+        <v>0.981987316197104</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9803784562427508</v>
+        <v>0.9853205559920679</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9785469749691323</v>
+        <v>0.9849674486474351</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9764283309013357</v>
+        <v>0.976295038724885</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9662101994238037</v>
+        <v>0.9618134283683166</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9659010551128073</v>
+        <v>0.9626295506416732</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.964466644217458</v>
+        <v>0.9625416245744004</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.971594735660568</v>
+        <v>0.9651027051296441</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.969432128559135</v>
+        <v>0.9655217570247315</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9698511804542223</v>
+        <v>0.9658968458861825</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9681062221723351</v>
+        <v>0.9589226250607999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9662527593818985</v>
+        <v>0.9613504134395929</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9699157219291353</v>
+        <v>0.9578413215100834</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9705559920679463</v>
+        <v>0.9553915516144722</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.968481311033786</v>
+        <v>0.9560538032701014</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9468977999775507</v>
+        <v>0.9560538032701014</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9449783926366595</v>
+        <v>0.9588346989935271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9449783926366595</v>
+        <v>0.9543981741310286</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9276995173420137</v>
+        <v>0.9560538032701014</v>
       </c>
     </row>
     <row r="59">
@@ -1010,977 +1010,977 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9280526246866465</v>
+        <v>0.9567160549257305</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9273683915141991</v>
+        <v>0.9533842182063083</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9302811763385341</v>
+        <v>0.9448642758259438</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9106184756987317</v>
+        <v>0.9413332023796162</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9106184756987317</v>
+        <v>0.8938643506566394</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9064031690799565</v>
+        <v>0.89035525872713</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8994509297713922</v>
+        <v>0.8868901298312568</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9008193961162869</v>
+        <v>0.8623732555094099</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7661755902271112</v>
+        <v>0.8761884049837243</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7431796497923449</v>
+        <v>0.869346073259251</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7438858644816104</v>
+        <v>0.8621960002993228</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.722787349870917</v>
+        <v>0.8597242488868935</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7193222209750439</v>
+        <v>0.8739364687394769</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7215287911101134</v>
+        <v>0.8353818236240506</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6755369102405807</v>
+        <v>0.8378096120028435</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6642580536536087</v>
+        <v>0.8257394208104165</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6300520073334082</v>
+        <v>0.8173527706065027</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6022238747334157</v>
+        <v>0.8140209338870805</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5835091854678789</v>
+        <v>0.8143740412317133</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.555966812586523</v>
+        <v>0.8239079395367981</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5560767201706139</v>
+        <v>0.8239079395367981</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5655886369588805</v>
+        <v>0.8096297751337598</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5655446739252441</v>
+        <v>0.8075111310659633</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5612854042728327</v>
+        <v>0.8071580237213305</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5627637782018184</v>
+        <v>0.8065397350993377</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5591887417218543</v>
+        <v>0.8016182137912972</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5585924346166797</v>
+        <v>0.8009339806188498</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5558555019268904</v>
+        <v>0.7733036816702211</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.544953137276911</v>
+        <v>0.7478359898230253</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5438498522093763</v>
+        <v>0.7498886893403675</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5441370150035545</v>
+        <v>0.7569508362330228</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5366544131402702</v>
+        <v>0.7498886893403675</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5616590900587421</v>
+        <v>0.7513231002357167</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5627403936094586</v>
+        <v>0.7513231002357167</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5627403936094586</v>
+        <v>0.7516762075803495</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5640209338870805</v>
+        <v>0.7204708721517566</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5570658884274329</v>
+        <v>0.7197646574624911</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5314649044037865</v>
+        <v>0.7190584427732256</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5351484453922999</v>
+        <v>0.7191903318741348</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.557728140083062</v>
+        <v>0.7191903318741348</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5726919407340891</v>
+        <v>0.7238027088711789</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5680136191865903</v>
+        <v>0.6322160175103828</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4990945485838291</v>
+        <v>0.6384840236464998</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4993817113780072</v>
+        <v>0.6384840236464998</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4993817113780072</v>
+        <v>0.6384840236464998</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4993817113780072</v>
+        <v>0.6406026677142964</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4997128372058218</v>
+        <v>0.6426993302652748</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4997128372058218</v>
+        <v>0.6239626594829198</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4997128372058218</v>
+        <v>0.6585891607737494</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4993597298611891</v>
+        <v>0.6653421633554084</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4996908556890036</v>
+        <v>0.6412649193699256</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4996908556890036</v>
+        <v>0.6409118120252928</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5000439630336364</v>
+        <v>0.618356905002432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5000439630336364</v>
+        <v>0.618356905002432</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5000439630336364</v>
+        <v>0.601760859804692</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5636252665843529</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5664940883750514</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5495669173494967</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5474043102480638</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5474043102480638</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4996688741721854</v>
+        <v>0.5815897781269876</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5866431885359374</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5841934186403263</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5817216672278969</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5644194073408912</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5877684551202903</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5722537134732667</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5722537134732667</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5722537134732667</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5672662476147716</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.5541573128297227</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5599609009615745</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4993377483443708</v>
+        <v>0.5621015265461893</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5807282897444531</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5722537134732667</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5772191978149437</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.582713641635799</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.5435818647809332</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.5272743854529127</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5231923710105886</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.5130167994911513</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5114065364612564</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5117596438058892</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5117596438058892</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4980791895835672</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4980791895835672</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4980791895835672</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4973509933774835</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.4980132450331126</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4980132450331126</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4986754966887417</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4986754966887417</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4996688741721854</v>
       </c>
     </row>
   </sheetData>
